--- a/site/exports/fdu-management.xlsx
+++ b/site/exports/fdu-management.xlsx
@@ -739,7 +739,7 @@
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L2" s="2" t="b">
@@ -806,7 +806,7 @@
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L3" s="2" t="b">
